--- a/Fixing the bug/Final results over different iterations/Final_results_over_different_iterations.xlsx
+++ b/Fixing the bug/Final results over different iterations/Final_results_over_different_iterations.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a1c0b903b3414e4/Desktop/Learning - post job/Time Series Forecasting/TFT - Study/Fixing the bug/Final results over different iterations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Final output by iterations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_10CA994EC6892531E4B5FA20C74B7567AA65015B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E339166-4F89-4E1A-A089-5890F340D3A0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" firstSheet="10" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Iteration 1" sheetId="1" r:id="rId1"/>
@@ -21,15 +20,24 @@
     <sheet name="Iteration 4" sheetId="10" r:id="rId6"/>
     <sheet name="Iteration 4 details" sheetId="13" r:id="rId7"/>
     <sheet name="Pivot" sheetId="12" r:id="rId8"/>
-    <sheet name="Actual sales over last 4 years" sheetId="3" r:id="rId9"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId10"/>
+    <sheet name="Iteration 5" sheetId="14" r:id="rId9"/>
+    <sheet name="Iteration 5 details" sheetId="15" r:id="rId10"/>
+    <sheet name="Iteration 6" sheetId="16" r:id="rId11"/>
+    <sheet name="Iteration 6 details" sheetId="17" r:id="rId12"/>
+    <sheet name="Iteration 7" sheetId="18" r:id="rId13"/>
+    <sheet name="Iteration 7 details" sheetId="19" r:id="rId14"/>
+    <sheet name="Iteration 8" sheetId="20" r:id="rId15"/>
+    <sheet name="Iteration 8 details" sheetId="21" r:id="rId16"/>
+    <sheet name="Actual sales over last 4 years" sheetId="3" r:id="rId17"/>
+    <sheet name="Business Expectations" sheetId="22" r:id="rId18"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Actual sales over last 4 years'!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Actual sales over last 4 years'!$A$1:$B$25</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId20"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="82">
   <si>
     <t>MONTH_NAME</t>
   </si>
@@ -92,18 +100,6 @@
     <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Output_of_June_to_Nov_forecast.csv</t>
   </si>
   <si>
-    <t>Month of sale</t>
-  </si>
-  <si>
-    <t>Actual sales</t>
-  </si>
-  <si>
-    <t>Name of month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">July </t>
-  </si>
-  <si>
     <t>Row Labels</t>
   </si>
   <si>
@@ -114,6 +110,15 @@
   </si>
   <si>
     <t>LAST_YEAR_SALES</t>
+  </si>
+  <si>
+    <t>TOTAL_MONTHLY_SALES_P10</t>
+  </si>
+  <si>
+    <t>TOTAL_MONTHLY_SALES_P50</t>
+  </si>
+  <si>
+    <t>TOTAL_MONTHLY_SALES_P90</t>
   </si>
   <si>
     <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\darts_logs\tft_engineered_features_6_month_with_modifications_2026-06-15_16_27_54</t>
@@ -146,12 +151,21 @@
     <t>AVG_MONTHLY_SALES_OVER_LAST_4_YEARS</t>
   </si>
   <si>
+    <t>PREDICTION_DEVIATION_FROM_AVERAGE</t>
+  </si>
+  <si>
+    <t>PREDICTION_DEVIATION_FROM_LAST_YEAR</t>
+  </si>
+  <si>
     <t>P50_DEVIATION_FROM_AVERAGE_SALES</t>
   </si>
   <si>
     <t>P90_DEVIATION_FROM_AVERAGE_SALES</t>
   </si>
   <si>
+    <t>P90_DEVIATON_FROM_LAST_MONTH_SALES</t>
+  </si>
+  <si>
     <t>P50_DEVIATON_FROM_LAST_YEAR_SALES</t>
   </si>
   <si>
@@ -167,36 +181,183 @@
     <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Huber loss\Final_output_Huber_Loss_June_to_November.csv</t>
   </si>
   <si>
-    <t>PREDICTIONS</t>
-  </si>
-  <si>
-    <t>P10_PREDICTION</t>
-  </si>
-  <si>
-    <t>P50_PREDICTION</t>
-  </si>
-  <si>
-    <t>P90_PREDICTION</t>
-  </si>
-  <si>
-    <t>P90_DEVIATON_FROM_LAST_YEAR_SALES</t>
-  </si>
-  <si>
-    <t>PREDICTION_DEVIATION_FROM_LAST_YEAR_SALES</t>
-  </si>
-  <si>
-    <t>PREDICTION_DEVIATION_FROM_AVERAGE_SALES</t>
+    <t>TOTAL_PREDICTED_SALES</t>
+  </si>
+  <si>
+    <t>DEVIATION_FROM_AVG_VALUE</t>
+  </si>
+  <si>
+    <t>DEVIATION_FROM_LAST_YEAR_VALUE</t>
+  </si>
+  <si>
+    <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Resolving_high_momentum_issue\With_festive_features_collapsed\darts_logs\tft_engineered_features_6_month_momentum_issue_fixing_2026-06-18_19_54_29</t>
+  </si>
+  <si>
+    <t>input_chunk_length = 12
+output_chunk_length = 6
+Training data - Apr'23 to Sep'25
+Val data - Oct'24 to May'26
+Lookback data - Jun'25 to May'26
+Lookahead data - June'26 to Nov'26
+Loss - QuantileLoss
+Epochs - 200
+Patience - 25
+Batch_size - 128
+with festive features collapsed</t>
+  </si>
+  <si>
+    <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Resolving_high_momentum_issue\With_festive_features_collapsed\Final_output_modified_timeframe_engineered_features.csv</t>
+  </si>
+  <si>
+    <t>TFT_TOTAL_SALES</t>
+  </si>
+  <si>
+    <t>ACTUAL_SALES</t>
+  </si>
+  <si>
+    <t>TFT_SALES_SERIES_A</t>
+  </si>
+  <si>
+    <t>AVG_TFT_SALES_SERIES_A</t>
+  </si>
+  <si>
+    <t>ACTUAL_AVG_SALES</t>
+  </si>
+  <si>
+    <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Modelling_after_updating_sales_numbers\Modelling\darts_logs\tft_uncollapsed_features_6_month_horizon_with_modifications_huber_loss_2026-06-24_23_27_49</t>
+  </si>
+  <si>
+    <t>input_chunk_length = 16
+output_chunk_length = 6
+Training data - Apr'23 to Sep'25
+Val data - Jun'24 to May'26
+Lookback data - Feb'25 to May'26
+Lookahead data - June'26 to Nov'26
+Loss - HuberLoss
+Epochs - 200
+Patience - 25
+Batch_size - 128
+without festive features collapsed</t>
+  </si>
+  <si>
+    <t>PREDICTED_SALES</t>
+  </si>
+  <si>
+    <t>Predicted Sales by the model</t>
+  </si>
+  <si>
+    <t>Total sales for the month from 2022 to 2025 as per actual data</t>
+  </si>
+  <si>
+    <t>Total sales for the month from 2022 to 2025 for all series as per TFT data</t>
+  </si>
+  <si>
+    <t>Total sales for the month from 2022 to 2025 for series A as per TFT data</t>
+  </si>
+  <si>
+    <t>Average sales for the month for series A as per TFT data over the past 4 years i.e., 2022 to 2025</t>
+  </si>
+  <si>
+    <t>Average sales for the month for series A as per actual data over the past 4 years i.e., 2022 to 2025</t>
+  </si>
+  <si>
+    <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Modelling_after_updating_sales_numbers\Modelling\Final_output_corrected_sales_data_Huber_Loss_June_to_November.csv</t>
+  </si>
+  <si>
+    <t>TOTAL_MONTHLY_SALES</t>
+  </si>
+  <si>
+    <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Final output by iterations\Iteration7_series_A_output.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Updated_diwali_features\Modelling\darts_logs\tft_diwali_based_features_6_month_horizon_huber_loss_2026-06-25_19_49_15</t>
+  </si>
+  <si>
+    <t>input_chunk_length = 16
+output_chunk_length = 6
+Training data - Apr'23 to Sep'25
+Val data - Jun'24 to May'26
+Lookback data - Feb'25 to May'26
+Lookahead data - June'26 to Nov'26
+Loss - HuberLoss
+Epochs - 200
+Patience - 25
+Batch_size - 128
+without festive features collapsed
+with Diwali D-30 to D+7 features : Mistakenly all features were fed as 1 for months</t>
+  </si>
+  <si>
+    <t>input_chunk_length = 16
+output_chunk_length = 6
+Training data - Apr'23 to Sep'25
+Val data - Jun'24 to May'26
+Lookback data - Feb'25 to May'26
+Lookahead data - June'26 to Nov'26
+Loss - HuberLoss
+Epochs - 200
+Patience - 25
+Batch_size - 128
+without festive features collapsed
+with Diwali D-30 to D+7 features : Correctly fed features</t>
+  </si>
+  <si>
+    <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Final output by iterations\Iteration8_series_A_output.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\G0004878\Desktop\TFT_Data\6_month_horizon\Updated_diwali_features\Modelling\darts_logs\tft_diwali_based_features_6_month_horizon_huber_loss_2026-06-26_15_04_06</t>
+  </si>
+  <si>
+    <t>EXPECTED_SALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">June </t>
+  </si>
+  <si>
+    <t>4.45L</t>
+  </si>
+  <si>
+    <t>3.9L</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>3.77L</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>3.67L</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>7.27L</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>13L</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>3.35L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,8 +380,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,6 +405,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -280,7 +455,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -307,8 +482,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -329,9 +515,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="YASH SAXENA" refreshedDate="46189.694878587965" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="24" xr:uid="{00000000-000A-0000-FFFF-FFFF03000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="YASH SAXENA" refreshedDate="46189.694878587965" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="24">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:D25" sheet="Actual sales over last 4 years"/>
+    <worksheetSource ref="A1:B25" sheet="Actual sales over last 4 years"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="Month of sale" numFmtId="17">
@@ -512,7 +698,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000000000000}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField numFmtId="17" showAll="0"/>
@@ -566,9 +752,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -836,7 +1019,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -863,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>10</v>
@@ -993,7 +1176,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E7">
+  <sortState ref="A2:E7">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1002,7 +1185,1135 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.6328125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="22.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="17">
+        <v>345295.74</v>
+      </c>
+      <c r="C2" s="17">
+        <v>1853233</v>
+      </c>
+      <c r="D2" s="17">
+        <v>1528736</v>
+      </c>
+      <c r="E2" s="17">
+        <v>1567474</v>
+      </c>
+      <c r="F2" s="17">
+        <v>313494.8</v>
+      </c>
+      <c r="G2" s="17">
+        <v>382184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="22">
+        <v>341688.8</v>
+      </c>
+      <c r="C3" s="17">
+        <v>1271432</v>
+      </c>
+      <c r="D3" s="17">
+        <v>1272270</v>
+      </c>
+      <c r="E3" s="17">
+        <v>1088060</v>
+      </c>
+      <c r="F3" s="17">
+        <v>217612</v>
+      </c>
+      <c r="G3" s="17">
+        <v>318067.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
+        <v>298721.28999999998</v>
+      </c>
+      <c r="C4" s="17">
+        <v>1265572</v>
+      </c>
+      <c r="D4" s="17">
+        <v>1266366</v>
+      </c>
+      <c r="E4" s="17">
+        <v>1083670</v>
+      </c>
+      <c r="F4" s="17">
+        <v>216734</v>
+      </c>
+      <c r="G4" s="17">
+        <v>316591.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="17">
+        <v>277160.65000000002</v>
+      </c>
+      <c r="C5" s="17">
+        <v>1137941</v>
+      </c>
+      <c r="D5" s="17">
+        <v>1138987</v>
+      </c>
+      <c r="E5" s="17">
+        <v>969897</v>
+      </c>
+      <c r="F5" s="17">
+        <v>193979.4</v>
+      </c>
+      <c r="G5" s="17">
+        <v>284746.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="17">
+        <v>910397.69</v>
+      </c>
+      <c r="C6" s="17">
+        <v>3917404</v>
+      </c>
+      <c r="D6" s="17">
+        <v>3920695</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3408688</v>
+      </c>
+      <c r="F6" s="17">
+        <v>681737.6</v>
+      </c>
+      <c r="G6" s="17">
+        <v>980173.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="17">
+        <v>630025.97</v>
+      </c>
+      <c r="C7" s="17">
+        <v>2341347</v>
+      </c>
+      <c r="D7" s="17">
+        <v>2342966</v>
+      </c>
+      <c r="E7" s="17">
+        <v>2137643</v>
+      </c>
+      <c r="F7" s="17">
+        <v>427528.6</v>
+      </c>
+      <c r="G7" s="17">
+        <v>585741.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.6328125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="22.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="17">
+        <v>279002.52</v>
+      </c>
+      <c r="C2" s="17">
+        <v>313494.8</v>
+      </c>
+      <c r="D2" s="17">
+        <v>382184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="17">
+        <v>248578.27</v>
+      </c>
+      <c r="C3" s="17">
+        <v>217612</v>
+      </c>
+      <c r="D3" s="17">
+        <v>318067.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
+        <v>220481.99</v>
+      </c>
+      <c r="C4" s="17">
+        <v>216734</v>
+      </c>
+      <c r="D4" s="17">
+        <v>316591.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="17">
+        <v>274768.95</v>
+      </c>
+      <c r="C5" s="17">
+        <v>193979.4</v>
+      </c>
+      <c r="D5" s="17">
+        <v>284746.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="17">
+        <v>1059753.8</v>
+      </c>
+      <c r="C6" s="17">
+        <v>681737.6</v>
+      </c>
+      <c r="D6" s="17">
+        <v>980173.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="17">
+        <v>987012.43</v>
+      </c>
+      <c r="C7" s="17">
+        <v>427528.6</v>
+      </c>
+      <c r="D7" s="17">
+        <v>585741.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.6328125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="22.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="17">
+        <v>309546</v>
+      </c>
+      <c r="C2" s="17">
+        <v>313494.8</v>
+      </c>
+      <c r="D2" s="17">
+        <v>382184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="17">
+        <v>293439</v>
+      </c>
+      <c r="C3" s="17">
+        <v>217612</v>
+      </c>
+      <c r="D3" s="17">
+        <v>318067.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
+        <v>261861</v>
+      </c>
+      <c r="C4" s="17">
+        <v>216734</v>
+      </c>
+      <c r="D4" s="17">
+        <v>316591.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="17">
+        <v>316906</v>
+      </c>
+      <c r="C5" s="17">
+        <v>193979.4</v>
+      </c>
+      <c r="D5" s="17">
+        <v>284746.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="17">
+        <v>976048</v>
+      </c>
+      <c r="C6" s="17">
+        <v>681737.6</v>
+      </c>
+      <c r="D6" s="17">
+        <v>980173.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="17">
+        <v>500643</v>
+      </c>
+      <c r="C7" s="17">
+        <v>427528.6</v>
+      </c>
+      <c r="D7" s="17">
+        <v>585741.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.6328125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="11">
+        <v>44652</v>
+      </c>
+      <c r="B2" s="1">
+        <v>438522</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11">
+        <v>44682</v>
+      </c>
+      <c r="B3" s="1">
+        <v>490743</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="11">
+        <v>44713</v>
+      </c>
+      <c r="B4" s="1">
+        <v>370885</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="11">
+        <v>44743</v>
+      </c>
+      <c r="B5" s="1">
+        <v>283269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="11">
+        <v>44774</v>
+      </c>
+      <c r="B6" s="1">
+        <v>289058</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="11">
+        <v>44805</v>
+      </c>
+      <c r="B7" s="1">
+        <v>267258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="11">
+        <v>44835</v>
+      </c>
+      <c r="B8" s="1">
+        <v>933981</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="11">
+        <v>44866</v>
+      </c>
+      <c r="B9" s="1">
+        <v>265440</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="11">
+        <v>44896</v>
+      </c>
+      <c r="B10" s="1">
+        <v>227350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="11">
+        <v>44927</v>
+      </c>
+      <c r="B11" s="1">
+        <v>329980</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="11">
+        <v>44958</v>
+      </c>
+      <c r="B12" s="1">
+        <v>335275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="11">
+        <v>44986</v>
+      </c>
+      <c r="B13" s="1">
+        <v>455771</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="11">
+        <v>45017</v>
+      </c>
+      <c r="B14" s="1">
+        <v>385724</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="11">
+        <v>45047</v>
+      </c>
+      <c r="B15" s="1">
+        <v>488509</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="11">
+        <v>45078</v>
+      </c>
+      <c r="B16" s="1">
+        <v>390658</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="11">
+        <v>45108</v>
+      </c>
+      <c r="B17" s="1">
+        <v>313426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="11">
+        <v>45139</v>
+      </c>
+      <c r="B18" s="1">
+        <v>339708</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="11">
+        <v>45170</v>
+      </c>
+      <c r="B19" s="1">
+        <v>298528</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="11">
+        <v>45200</v>
+      </c>
+      <c r="B20" s="1">
+        <v>480276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="11">
+        <v>45231</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1033206</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="11">
+        <v>45261</v>
+      </c>
+      <c r="B22" s="1">
+        <v>242937</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="11">
+        <v>45292</v>
+      </c>
+      <c r="B23" s="1">
+        <v>353608</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="11">
+        <v>45323</v>
+      </c>
+      <c r="B24" s="1">
+        <v>373163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="11">
+        <v>45352</v>
+      </c>
+      <c r="B25" s="1">
+        <v>436902</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="11">
+        <v>45383</v>
+      </c>
+      <c r="B26" s="1">
+        <v>499719</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="11">
+        <v>45413</v>
+      </c>
+      <c r="B27" s="1">
+        <v>402173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="11">
+        <v>45444</v>
+      </c>
+      <c r="B28" s="1">
+        <v>394727</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="11">
+        <v>45474</v>
+      </c>
+      <c r="B29" s="1">
+        <v>359215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="11">
+        <v>45505</v>
+      </c>
+      <c r="B30" s="1">
+        <v>314336</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="11">
+        <v>45536</v>
+      </c>
+      <c r="B31" s="1">
+        <v>182060</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="11">
+        <v>45566</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1161951</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="11">
+        <v>45597</v>
+      </c>
+      <c r="B33" s="1">
+        <v>591266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="11">
+        <v>45627</v>
+      </c>
+      <c r="B34" s="1">
+        <v>233667</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="11">
+        <v>45658</v>
+      </c>
+      <c r="B35" s="1">
+        <v>357236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="11">
+        <v>45689</v>
+      </c>
+      <c r="B36" s="1">
+        <v>357233</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="11">
+        <v>45717</v>
+      </c>
+      <c r="B37" s="1">
+        <v>409785</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="11">
+        <v>45748</v>
+      </c>
+      <c r="B38" s="1">
+        <v>480802</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="11">
+        <v>45778</v>
+      </c>
+      <c r="B39" s="1">
+        <v>459630</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="11">
+        <v>45809</v>
+      </c>
+      <c r="B40" s="1">
+        <v>372466</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="11">
+        <v>45839</v>
+      </c>
+      <c r="B41" s="1">
+        <v>316360</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="11">
+        <v>45870</v>
+      </c>
+      <c r="B42" s="1">
+        <v>323264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="11">
+        <v>45901</v>
+      </c>
+      <c r="B43" s="1">
+        <v>391141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="11">
+        <v>45931</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1344487</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="11">
+        <v>45962</v>
+      </c>
+      <c r="B45" s="1">
+        <v>453054</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="11">
+        <v>45992</v>
+      </c>
+      <c r="B46" s="1">
+        <v>286475</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="11">
+        <v>46023</v>
+      </c>
+      <c r="B47" s="1">
+        <v>461703</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="11">
+        <v>46054</v>
+      </c>
+      <c r="B48" s="1">
+        <v>433089</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="11">
+        <v>46082</v>
+      </c>
+      <c r="B49" s="1">
+        <v>532533</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="11">
+        <v>46113</v>
+      </c>
+      <c r="B50" s="1">
+        <v>556122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="11">
+        <v>46143</v>
+      </c>
+      <c r="B51" s="1">
+        <v>466601</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="11">
+        <v>46174</v>
+      </c>
+      <c r="B52" s="1">
+        <v>343628</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:B52">
+    <sortCondition ref="A1"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
@@ -1011,12 +2322,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" customWidth="1"/>
     <col min="3" max="3" width="17.453125" customWidth="1"/>
     <col min="4" max="4" width="19.90625" customWidth="1"/>
     <col min="5" max="5" width="17.90625" customWidth="1"/>
@@ -1028,151 +2339,151 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>43</v>
+      <c r="F1" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="17">
         <v>416260</v>
       </c>
-      <c r="C2" s="14">
-        <v>407552.5</v>
-      </c>
-      <c r="D2" s="14">
-        <v>381884</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="17">
+        <v>444836</v>
+      </c>
+      <c r="D2" s="17">
+        <v>401428</v>
+      </c>
+      <c r="E2" s="4">
         <f>(B2-C2)/C2</f>
-        <v>2.1365345568975777E-2</v>
+        <v>-6.423940508412089E-2</v>
       </c>
       <c r="F2" s="4">
         <f>(B2-D2)/D2</f>
-        <v>9.0016863759675714E-2</v>
+        <v>3.6948095299779785E-2</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="17">
         <v>335549</v>
       </c>
-      <c r="C3" s="14">
-        <v>344535</v>
-      </c>
-      <c r="D3" s="14">
-        <v>306235</v>
+      <c r="C3" s="17">
+        <v>375676.75</v>
+      </c>
+      <c r="D3" s="17">
+        <v>328748</v>
       </c>
       <c r="E3" s="4">
         <f t="shared" ref="E3:E7" si="0">(B3-C3)/C3</f>
-        <v>-2.6081530178356335E-2</v>
+        <v>-0.10681456864179112</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" ref="F3:F7" si="1">(B3-D3)/D3</f>
-        <v>9.5723872189658263E-2</v>
+        <v>2.0687578327472714E-2</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="17">
         <v>294277.58</v>
       </c>
-      <c r="C4" s="14">
-        <v>341248.5</v>
-      </c>
-      <c r="D4" s="14">
-        <v>304119</v>
+      <c r="C4" s="17">
+        <v>373306.5</v>
+      </c>
+      <c r="D4" s="17">
+        <v>331076</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13764432664172879</v>
+        <v>-0.2116998230676401</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="1"/>
-        <v>-3.2360424702172451E-2</v>
+        <v>-0.11114795394410946</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="17">
         <v>264781.59000000003</v>
       </c>
-      <c r="C5" s="14">
-        <v>296994</v>
-      </c>
-      <c r="D5" s="14">
-        <v>358049</v>
+      <c r="C5" s="17">
+        <v>327632</v>
+      </c>
+      <c r="D5" s="17">
+        <v>395829</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.10846148407038518</v>
+        <v>-0.19183233017531856</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
-        <v>-0.26048783825677485</v>
+        <v>-0.33107076540627384</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="17">
         <v>1234498.6299999999</v>
       </c>
-      <c r="C6" s="14">
-        <v>1032598.5</v>
-      </c>
-      <c r="D6" s="14">
-        <v>1255219</v>
+      <c r="C6" s="17">
+        <v>1121534.25</v>
+      </c>
+      <c r="D6" s="17">
+        <v>1353626</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>0.19552626698566761</v>
+        <v>0.10072307644639465</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="1"/>
-        <v>-1.6507374410361948E-2</v>
+        <v>-8.8006118381295947E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="17">
         <v>852511.24</v>
       </c>
-      <c r="C7" s="14">
-        <v>678201.25</v>
-      </c>
-      <c r="D7" s="14">
-        <v>411370</v>
+      <c r="C7" s="17">
+        <v>720126.75</v>
+      </c>
+      <c r="D7" s="17">
+        <v>454356</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
-        <v>0.25701809013180082</v>
+        <v>0.18383498460514067</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" si="1"/>
-        <v>1.0723709555874275</v>
+        <v>0.87630677266284585</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +2492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1193,23 +2504,23 @@
       <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
+      <c r="B1" s="15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
+      <c r="B2" s="15" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1219,12 +2530,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="3" max="3" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.81640625" customWidth="1"/>
     <col min="5" max="5" width="16.7265625" customWidth="1"/>
     <col min="6" max="6" width="15.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.54296875" customWidth="1"/>
@@ -1238,50 +2551,50 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="17">
         <v>131204.63</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="17">
         <v>350815.9</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="17">
         <v>787673.46</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="17">
         <v>407552.5</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="17">
         <v>381884</v>
       </c>
       <c r="G2" s="3">
@@ -1305,19 +2618,19 @@
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="17">
         <v>102561.08</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="17">
         <v>287514.03000000003</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="17">
         <v>636907.5</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="17">
         <v>344535</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="17">
         <v>306235</v>
       </c>
       <c r="G3" s="3">
@@ -1341,19 +2654,19 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="17">
         <v>82101.070000000007</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="17">
         <v>247342.42</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="17">
         <v>571675.73</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="17">
         <v>341248.5</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="17">
         <v>304119</v>
       </c>
       <c r="G4" s="3">
@@ -1377,19 +2690,19 @@
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="17">
         <v>79906.649999999994</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="17">
         <v>215034.39</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="17">
         <v>515230.48</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="17">
         <v>296994</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="17">
         <v>358049</v>
       </c>
       <c r="G5" s="3">
@@ -1413,19 +2726,19 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="17">
         <v>538560.4</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="17">
         <v>1303352.69</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="17">
         <v>1832653.55</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="17">
         <v>1032598.5</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="17">
         <v>1255219</v>
       </c>
       <c r="G6" s="3">
@@ -1449,19 +2762,19 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="17">
         <v>209857.03</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="17">
         <v>724978.81</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="17">
         <v>1646160.12</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="17">
         <v>678201.25</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="17">
         <v>411370</v>
       </c>
       <c r="G7" s="3">
@@ -1488,20 +2801,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="126.6328125" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.6328125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
+      <c r="B1" s="15" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1509,15 +2823,15 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>25</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +2840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1543,32 +2857,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>43</v>
+        <v>19</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="17">
         <v>507212.74</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="17">
         <v>407552.5</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="17">
         <v>381884</v>
       </c>
       <c r="E2" s="4">
@@ -1584,13 +2898,13 @@
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="17">
         <v>404020.1</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="17">
         <v>344535</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="17">
         <v>306235</v>
       </c>
       <c r="E3" s="4">
@@ -1606,13 +2920,13 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="17">
         <v>368491.51</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="17">
         <v>341248.5</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="17">
         <v>304119</v>
       </c>
       <c r="E4" s="4">
@@ -1628,13 +2942,13 @@
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="17">
         <v>338404.08</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="17">
         <v>296994</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="17">
         <v>358049</v>
       </c>
       <c r="E5" s="4">
@@ -1650,13 +2964,13 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="17">
         <v>1283292.08</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="17">
         <v>1032598.5</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="17">
         <v>1255219</v>
       </c>
       <c r="E6" s="4">
@@ -1672,13 +2986,13 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="17">
         <v>671600.19</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="17">
         <v>678201.25</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="17">
         <v>411370</v>
       </c>
       <c r="E7" s="4">
@@ -1697,20 +3011,21 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="126.6328125" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.6328125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
+      <c r="B1" s="15" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1718,15 +3033,15 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +3050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1745,17 +3060,17 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="13">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="14">
         <v>407552.5</v>
       </c>
     </row>
@@ -1763,7 +3078,7 @@
       <c r="A5" s="13">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="14">
         <v>344535</v>
       </c>
     </row>
@@ -1771,7 +3086,7 @@
       <c r="A6" s="13">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="14">
         <v>341248.5</v>
       </c>
     </row>
@@ -1779,7 +3094,7 @@
       <c r="A7" s="13">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="14">
         <v>296994</v>
       </c>
     </row>
@@ -1787,7 +3102,7 @@
       <c r="A8" s="13">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="14">
         <v>1032598.5</v>
       </c>
     </row>
@@ -1795,15 +3110,15 @@
       <c r="A9" s="13">
         <v>11</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="14">
         <v>678201.25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10">
+        <v>17</v>
+      </c>
+      <c r="B10" s="14">
         <v>516854.95833333331</v>
       </c>
     </row>
@@ -1813,375 +3128,115 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="11">
-        <v>44713</v>
-      </c>
-      <c r="B2" s="1">
-        <v>323008</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1">
+      <c r="B2" s="17">
+        <v>334153.74</v>
+      </c>
+      <c r="C2" s="17">
+        <v>407552.5</v>
+      </c>
+      <c r="D2" s="17">
+        <v>381884</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="17">
+        <v>303849.09999999998</v>
+      </c>
+      <c r="C3" s="17">
+        <v>344535</v>
+      </c>
+      <c r="D3" s="17">
+        <v>306235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
+        <v>315653.51</v>
+      </c>
+      <c r="C4" s="17">
+        <v>341248.5</v>
+      </c>
+      <c r="D4" s="17">
+        <v>304119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="17">
+        <v>309522</v>
+      </c>
+      <c r="C5" s="17">
+        <v>296994</v>
+      </c>
+      <c r="D5" s="17">
+        <v>358049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="11">
-        <v>44743</v>
-      </c>
-      <c r="B3" s="1">
-        <v>252443</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="11">
-        <v>44774</v>
-      </c>
-      <c r="B4" s="1">
-        <v>257380</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="11">
-        <v>44805</v>
-      </c>
-      <c r="B5" s="1">
-        <v>240072</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="11">
-        <v>44835</v>
-      </c>
-      <c r="B6" s="1">
-        <v>836463</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="11">
-        <v>44866</v>
-      </c>
-      <c r="B7" s="1">
-        <v>242653</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B6" s="17">
+        <v>944853</v>
+      </c>
+      <c r="C6" s="17">
+        <v>1032598.5</v>
+      </c>
+      <c r="D6" s="17">
+        <v>1255219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="11">
-        <v>45078</v>
-      </c>
-      <c r="B8" s="1">
-        <v>431597</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="11">
-        <v>45108</v>
-      </c>
-      <c r="B9" s="1">
-        <v>368892</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="11">
-        <v>45139</v>
-      </c>
-      <c r="B10" s="1">
-        <v>407427</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="11">
-        <v>45170</v>
-      </c>
-      <c r="B11" s="1">
-        <v>364989</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="11">
-        <v>45200</v>
-      </c>
-      <c r="B12" s="1">
-        <v>587473</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="11">
-        <v>45231</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1298116</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="11">
-        <v>45444</v>
-      </c>
-      <c r="B14" s="1">
-        <v>493721</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="11">
-        <v>45474</v>
-      </c>
-      <c r="B15" s="1">
-        <v>450570</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="11">
-        <v>45505</v>
-      </c>
-      <c r="B16" s="1">
-        <v>396068</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="11">
-        <v>45536</v>
-      </c>
-      <c r="B17" s="1">
-        <v>224866</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="11">
-        <v>45566</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1451239</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="11">
-        <v>45597</v>
-      </c>
-      <c r="B19" s="1">
-        <v>760666</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="11">
-        <v>45809</v>
-      </c>
-      <c r="B20" s="1">
-        <v>381884</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="11">
-        <v>45839</v>
-      </c>
-      <c r="B21" s="1">
-        <v>306235</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="11">
-        <v>45870</v>
-      </c>
-      <c r="B22" s="1">
-        <v>304119</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="11">
-        <v>45901</v>
-      </c>
-      <c r="B23" s="1">
-        <v>358049</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="11">
-        <v>45931</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1255219</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="11">
-        <v>45962</v>
-      </c>
-      <c r="B25" s="1">
+      <c r="B7" s="17">
+        <v>755166</v>
+      </c>
+      <c r="C7" s="17">
+        <v>678201.25</v>
+      </c>
+      <c r="D7" s="17">
         <v>411370</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="1">
-        <v>11</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D25" xr:uid="{00000000-0009-0000-0000-000008000000}">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2025" dateTimeGrouping="year"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>